--- a/Send_Threaded_Message/Send_Threaded_Message_Test_Cases.xlsx
+++ b/Send_Threaded_Message/Send_Threaded_Message_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1821,6 +1821,706 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>STM_039</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Integration: Thread with Message List</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread reply count updates in main message list</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>1. Reply in a thread.
+2. Close thread.
+3. Observe parent message in main chat.</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Parent message should show updated reply count. Clicking count should reopen thread.</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>STM_040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Integration: Thread with Notifications</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread reply triggers notification for thread participants</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>1. User A replies in a thread.
+2. Check User B's notifications (who also replied in thread).</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>User B should receive notification for the new thread reply.</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>STM_041</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Integration: Thread with Conversation List</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread reply updates conversation list preview</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>1. Reply in a thread.
+2. Check conversation list.</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Conversation preview should update to reflect the thread activity.</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>STM_042</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Regression: Threaded Message</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and thread is open</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread intact after editing parent message</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>1. Edit the parent message of a thread.
+2. Open thread.</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Thread should remain intact. Parent message should show edited content. All replies preserved.</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>STM_043</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread behavior after deleting parent message</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>1. Delete the parent message that has a thread.</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Thread should be handled per policy — either deleted with parent or preserved with 'deleted message' parent.</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>STM_044</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr"/>
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread after app restart</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a thread.
+2. Close and reopen app.
+3. Navigate back to thread.</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Thread should load with all previous replies intact.</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>STM_045</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Security: Threaded Message</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread messages only visible to conversation participants</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as a non-participant.
+2. Try to access thread messages.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Thread messages should not be accessible to non-participants of the conversation.</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>STM_046</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr"/>
+      <c r="D47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Verify XSS prevention in thread messages</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>1. Send '&lt;img src=x onerror=alert(1)&gt;' in a thread reply.</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>HTML should be escaped. No script execution.</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>STM_047</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread message cannot be sent after being removed from group</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>1. Get removed from a group.
+2. Try to send a thread reply in that group.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Message should fail with appropriate error.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>STM_048</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case: Threaded Message</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and thread is open</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread with 500+ replies</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a thread with 500+ replies.
+2. Scroll through.</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>All replies should load via pagination. No performance issues.</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>STM_049</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Verify nested thread behavior (reply to a thread reply)</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>1. Try to reply to a specific message within a thread.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Should either allow nested reply or keep flat thread structure per design.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>STM_050</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr"/>
+      <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread with mixed media types</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>1. Send text, image, video, audio, and document in the same thread.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>All message types should display correctly within the thread.</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>STM_051</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread reply during network interruption</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>1. Start sending a thread reply.
+2. Disconnect network mid-send.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Message should show failed state with retry option. No partial/corrupted messages.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>STM_052</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Boundary: Threaded Message</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and thread is open</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread with exactly 1 reply</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>1. Reply once in a thread.
+2. Observe thread and parent message.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Thread should show 1 reply. Parent message should show '1 Reply'.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>STM_053</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread reply with exactly 1 character</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>1. Send 'a' as a thread reply.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Single character reply should display correctly in thread.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>STM_054</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr"/>
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread reply at max character limit</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a thread reply at exactly the maximum character limit.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Reply should send successfully.</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>STM_055</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning: Thread Contexts</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread on a text message</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>1. Start a thread on a text message.
+2. Reply.</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Thread should work correctly with text parent message.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>STM_056</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread on an image message</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>1. Start a thread on an image message.
+2. Reply.</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Thread should work correctly with image as parent. Image should display in thread header.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>STM_057</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread on a video message</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>1. Start a thread on a video message.
+2. Reply.</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Thread should work correctly with video as parent.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>STM_058</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr"/>
+      <c r="D59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread on a document message</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>1. Start a thread on a document message.
+2. Reply.</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Thread should work correctly with document as parent.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Send_Threaded_Message/Send_Threaded_Message_Test_Cases.xlsx
+++ b/Send_Threaded_Message/Send_Threaded_Message_Test_Cases.xlsx
@@ -7,7 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Threaded Message Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Functional" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Integration" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Regression" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Security" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Edge Cases" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Boundary Values" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Equivalence Partitioning" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,10 +439,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -540,9 +547,9 @@
           <t>STM_002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify thread panel shows parent message</t>
@@ -570,9 +577,9 @@
           <t>STM_003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify thread composer input field</t>
@@ -601,9 +608,9 @@
           <t>STM_004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify thread panel close button</t>
@@ -632,9 +639,9 @@
           <t>STM_005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify thread reply count on parent message</t>
@@ -707,9 +714,9 @@
           <t>STM_007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Verify Enter key sends message in thread</t>
@@ -739,9 +746,9 @@
           <t>STM_008</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Verify multiple text messages in thread</t>
@@ -769,9 +776,9 @@
           <t>STM_009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Verify thread message shows sender info</t>
@@ -800,9 +807,9 @@
           <t>STM_010</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr"/>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Verify long text message in thread</t>
@@ -831,9 +838,9 @@
           <t>STM_011</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr"/>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Verify emoji message in thread</t>
@@ -905,8 +912,8 @@
           <t>STM_013</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr"/>
-      <c r="C14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
@@ -983,9 +990,9 @@
           <t>STM_015</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Verify sending image in thread</t>
@@ -1016,9 +1023,9 @@
           <t>STM_016</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr"/>
-      <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Verify sending video in thread</t>
@@ -1049,9 +1056,9 @@
           <t>STM_017</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr"/>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Verify sending audio in thread</t>
@@ -1082,9 +1089,9 @@
           <t>STM_018</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr"/>
-      <c r="C19" s="2" t="inlineStr"/>
-      <c r="D19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Verify sending document in thread</t>
@@ -1115,9 +1122,9 @@
           <t>STM_019</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr"/>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Verify image preview in thread</t>
@@ -1146,9 +1153,9 @@
           <t>STM_020</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr"/>
-      <c r="C21" s="2" t="inlineStr"/>
-      <c r="D21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Verify video playback in thread</t>
@@ -1220,8 +1227,8 @@
           <t>STM_022</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr"/>
-      <c r="C23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
@@ -1255,8 +1262,8 @@
           <t>STM_023</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr"/>
-      <c r="C24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
           <t>User is logged in and thread is open</t>
@@ -1333,9 +1340,9 @@
           <t>STM_025</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr"/>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Verify sending GIF in thread</t>
@@ -1365,9 +1372,9 @@
           <t>STM_026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr"/>
-      <c r="C27" s="2" t="inlineStr"/>
-      <c r="D27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Verify sending location in thread (if supported)</t>
@@ -1439,9 +1446,9 @@
           <t>STM_028</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr"/>
-      <c r="C29" s="2" t="inlineStr"/>
-      <c r="D29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Verify thread reply count updates in real-time</t>
@@ -1513,9 +1520,9 @@
           <t>STM_030</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr"/>
-      <c r="C31" s="2" t="inlineStr"/>
-      <c r="D31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Verify delete own message in thread</t>
@@ -1545,9 +1552,9 @@
           <t>STM_031</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr"/>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Verify edit own message in thread</t>
@@ -1577,9 +1584,9 @@
           <t>STM_032</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr"/>
-      <c r="C33" s="2" t="inlineStr"/>
-      <c r="D33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Verify react to message in thread</t>
@@ -1651,9 +1658,9 @@
           <t>STM_034</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr"/>
-      <c r="C35" s="2" t="inlineStr"/>
-      <c r="D35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Verify cannot delete others' messages in thread</t>
@@ -1726,7 +1733,7 @@
           <t>STM_036</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="n"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Verify Thread in Group Chat</t>
@@ -1766,9 +1773,9 @@
           <t>STM_037</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr"/>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Verify multiple users can reply in same thread</t>
@@ -1796,9 +1803,9 @@
           <t>STM_038</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr"/>
-      <c r="C39" s="2" t="inlineStr"/>
-      <c r="D39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Verify thread scroll with many replies</t>
@@ -1821,701 +1828,1103 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>STM_039</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Integration: Thread with Message List</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify thread reply count updates in main message list</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Reply in a thread.
 2. Close thread.
 3. Observe parent message in main chat.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Parent message should show updated reply count. Clicking count should reopen thread.</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>STM_040</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr"/>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Integration: Thread with Notifications</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr"/>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify thread reply triggers notification for thread participants</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. User A replies in a thread.
 2. Check User B's notifications (who also replied in thread).</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>User B should receive notification for the new thread reply.</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>STM_041</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr"/>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Integration: Thread with Conversation List</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify thread reply updates conversation list preview</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Reply in a thread.
 2. Check conversation list.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Conversation preview should update to reflect the thread activity.</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FFC000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>STM_042</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Regression: Threaded Message</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in and thread is open</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify thread intact after editing parent message</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Edit the parent message of a thread.
 2. Open thread.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Thread should remain intact. Parent message should show edited content. All replies preserved.</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>STM_043</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr"/>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify thread behavior after deleting parent message</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Delete the parent message that has a thread.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Thread should be handled per policy — either deleted with parent or preserved with 'deleted message' parent.</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>STM_044</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr"/>
-      <c r="C45" s="2" t="inlineStr"/>
-      <c r="D45" s="2" t="inlineStr"/>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify thread after app restart</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Open a thread.
 2. Close and reopen app.
 3. Navigate back to thread.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Thread should load with all previous replies intact.</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FF0000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>STM_045</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Security: Threaded Message</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify thread messages only visible to conversation participants</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Login as a non-participant.
 2. Try to access thread messages.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Thread messages should not be accessible to non-participants of the conversation.</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>STM_046</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr"/>
-      <c r="C47" s="2" t="inlineStr"/>
-      <c r="D47" s="2" t="inlineStr"/>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify XSS prevention in thread messages</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Send '&lt;img src=x onerror=alert(1)&gt;' in a thread reply.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>HTML should be escaped. No script execution.</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>STM_047</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr"/>
-      <c r="C48" s="2" t="inlineStr"/>
-      <c r="D48" s="2" t="inlineStr"/>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify thread message cannot be sent after being removed from group</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Get removed from a group.
 2. Try to send a thread reply in that group.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Message should fail with appropriate error.</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>STM_048</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Edge Case: Threaded Message</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in and thread is open</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify thread with 500+ replies</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Open a thread with 500+ replies.
 2. Scroll through.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>All replies should load via pagination. No performance issues.</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>STM_049</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr"/>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr"/>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify nested thread behavior (reply to a thread reply)</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Try to reply to a specific message within a thread.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Should either allow nested reply or keep flat thread structure per design.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>STM_050</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr"/>
-      <c r="C51" s="2" t="inlineStr"/>
-      <c r="D51" s="2" t="inlineStr"/>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify thread with mixed media types</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Send text, image, video, audio, and document in the same thread.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>All message types should display correctly within the thread.</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>STM_051</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr"/>
-      <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify thread reply during network interruption</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Start sending a thread reply.
 2. Disconnect network mid-send.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Message should show failed state with retry option. No partial/corrupted messages.</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>STM_052</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Boundary: Threaded Message</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in and thread is open</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify thread with exactly 1 reply</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Reply once in a thread.
 2. Observe thread and parent message.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Thread should show 1 reply. Parent message should show '1 Reply'.</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>STM_053</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr"/>
-      <c r="C54" s="2" t="inlineStr"/>
-      <c r="D54" s="2" t="inlineStr"/>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify thread reply with exactly 1 character</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Send 'a' as a thread reply.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Single character reply should display correctly in thread.</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>STM_054</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr"/>
-      <c r="C55" s="2" t="inlineStr"/>
-      <c r="D55" s="2" t="inlineStr"/>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify thread reply at max character limit</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Send a thread reply at exactly the maximum character limit.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Reply should send successfully.</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0000B0F0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>STM_055</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Thread Contexts</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify thread on a text message</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Start a thread on a text message.
 2. Reply.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Thread should work correctly with text parent message.</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>STM_056</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr"/>
-      <c r="C57" s="2" t="inlineStr"/>
-      <c r="D57" s="2" t="inlineStr"/>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify thread on an image message</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Start a thread on an image message.
 2. Reply.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Thread should work correctly with image as parent. Image should display in thread header.</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>STM_057</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr"/>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="2" t="inlineStr"/>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify thread on a video message</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Start a thread on a video message.
 2. Reply.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Thread should work correctly with video as parent.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>STM_058</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr"/>
-      <c r="C59" s="2" t="inlineStr"/>
-      <c r="D59" s="2" t="inlineStr"/>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify thread on a document message</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Start a thread on a document message.
 2. Reply.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Thread should work correctly with document as parent.</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>

--- a/Send_Threaded_Message/Send_Threaded_Message_Test_Cases.xlsx
+++ b/Send_Threaded_Message/Send_Threaded_Message_Test_Cases.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -863,142 +863,162 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>STM_012</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Verify Send Text Message in Thread</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>User is logged in and thread is open</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Verify empty message not sent in thread</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1. Open a thread.
 2. Leave input empty.
 3. Click send.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Empty message should not be sent. Send button should be disabled or no action.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>STM_013</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Verify text message fails in thread without network</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Try to send text message in thread.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Error message should display or message should queue with retry option.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>STM_014</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Verify Send Media in Thread</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and thread is open</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Verify attach button available in thread composer</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a thread.
-2. Observe thread composer.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Attach/attachment button should be available in the thread input area.</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>STM_015</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="n"/>
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>STM_014</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Verify Send Media in Thread</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and thread is open</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Verify attach button available in thread composer</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a thread.
+2. Observe thread composer.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Attach/attachment button should be available in the thread input area.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>STM_015</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Verify sending image in thread</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>1. Open a thread.
 2. Click attach.
@@ -1006,32 +1026,32 @@
 4. Send.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Image should upload and display in the thread with thumbnail.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>STM_016</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Verify sending video in thread</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>1. Open a thread.
 2. Click attach.
@@ -1039,32 +1059,32 @@
 4. Send.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Video should upload and display in the thread with thumbnail and play icon.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>STM_017</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Verify sending audio in thread</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1. Open a thread.
 2. Click attach or record.
@@ -1072,32 +1092,32 @@
 4. Send.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Audio message should display in thread with play button and duration.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>STM_018</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Verify sending document in thread</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Open a thread.
 2. Click attach.
@@ -1105,407 +1125,279 @@
 4. Send.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>Document should upload and display with file icon, name, and size in thread.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>STM_019</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Verify image preview in thread</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>1. Send an image in thread.
 2. Tap on the image thumbnail.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Full-size image preview should open.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>STM_020</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Verify video playback in thread</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. Send a video in thread.
 2. Tap play on the video.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Video should play within the thread or in a media player.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>STM_021</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Verify Send Media in Thread</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>User is logged in and thread is open</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Verify file size limit in thread</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. Open a thread.
 2. Try to attach a file exceeding size limit.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Error message should display indicating file size limit exceeded.</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>STM_022</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Verify media upload fails in thread without network</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Try to send media in thread.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Error message should display or upload should queue with retry option.</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>STM_023</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>User is logged in and thread is open</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Verify unsupported file type in thread</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1. Try to attach an unsupported file type in thread.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Error message should display or file type should be rejected.</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>STM_024</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Verify Send Custom Message in Thread</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>User is logged in and thread is open</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Verify sending sticker in thread</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. Open a thread.
 2. Open sticker picker.
 3. Select a sticker.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>Sticker should be sent and display in the thread.</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>STM_025</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Verify sending GIF in thread</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>1. Open a thread.
 2. Open GIF picker.
 3. Select a GIF.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>GIF should be sent and display/animate in the thread.</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>STM_026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Verify sending location in thread (if supported)</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a thread.
-2. Share location.</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Location message with map preview should display in the thread.</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>STM_027</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Verify Thread Notifications</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and has participated in a thread</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Verify notification for new thread reply</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1. Another user replies in a thread you participated in.
-2. Observe notifications.</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Notification should appear for the new thread reply.</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>STM_028</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Verify thread reply count updates in real-time</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1. Be on main chat.
-2. Another user replies in a thread.</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Reply count on parent message should update in real-time.</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>STM_029</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Verify Thread Message Actions</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and thread is open</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Verify copy message in thread</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>1. Long press on a text message in thread.
-2. Select 'Copy'.</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Message text should be copied to clipboard.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1517,7 +1409,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>STM_030</t>
+          <t>STM_026</t>
         </is>
       </c>
       <c r="B31" s="2" t="n"/>
@@ -1525,51 +1417,61 @@
       <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Verify delete own message in thread</t>
+          <t>Verify sending location in thread (if supported)</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1. Long press on own message in thread.
-2. Select 'Delete'.
-3. Confirm.</t>
+          <t>1. Open a thread.
+2. Share location.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Message should be deleted from the thread. Reply count should update.</t>
+          <t>Location message with map preview should display in the thread.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>STM_031</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
+          <t>STM_027</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Verify Thread Notifications</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and has participated in a thread</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Verify edit own message in thread</t>
+          <t>Verify notification for new thread reply</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1. Long press on own text message in thread.
-2. Select 'Edit'.
-3. Modify and save.</t>
+          <t>1. Another user replies in a thread you participated in.
+2. Observe notifications.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Message should update with new text and show 'edited' indicator.</t>
+          <t>Notification should appear for the new thread reply.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1581,7 +1483,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>STM_032</t>
+          <t>STM_028</t>
         </is>
       </c>
       <c r="B33" s="2" t="n"/>
@@ -1589,35 +1491,35 @@
       <c r="D33" s="2" t="n"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Verify react to message in thread</t>
+          <t>Verify thread reply count updates in real-time</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1. Long press on a message in thread.
-2. Select a reaction.</t>
+          <t>1. Be on main chat.
+2. Another user replies in a thread.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Reaction should appear below the message in the thread.</t>
+          <t>Reply count on parent message should update in real-time.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>STM_033</t>
+          <t>STM_029</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1632,30 +1534,30 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Verify cannot edit others' messages in thread</t>
+          <t>Verify copy message in thread</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1. Long press on another user's message in thread.
-2. Observe menu.</t>
+          <t>1. Long press on a text message in thread.
+2. Select 'Copy'.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>'Edit' option should NOT be available for other users' messages.</t>
+          <t>Message text should be copied to clipboard.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>STM_034</t>
+          <t>STM_030</t>
         </is>
       </c>
       <c r="B35" s="2" t="n"/>
@@ -1663,166 +1565,324 @@
       <c r="D35" s="2" t="n"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Verify cannot delete others' messages in thread</t>
+          <t>Verify delete own message in thread</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>1. Long press on own message in thread.
+2. Select 'Delete'.
+3. Confirm.</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Message should be deleted from the thread. Reply count should update.</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>STM_031</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Verify edit own message in thread</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>1. Long press on own text message in thread.
+2. Select 'Edit'.
+3. Modify and save.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Message should update with new text and show 'edited' indicator.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>STM_032</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Verify react to message in thread</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>1. Long press on a message in thread.
+2. Select a reaction.</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Reaction should appear below the message in the thread.</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>STM_033</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Verify Thread Message Actions</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and thread is open</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Verify cannot edit others' messages in thread</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>1. Long press on another user's message in thread.
 2. Observe menu.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>'Edit' option should NOT be available for other users' messages.</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>STM_034</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Verify cannot delete others' messages in thread</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>1. Long press on another user's message in thread.
+2. Observe menu.</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>'Delete' option should NOT be available for other users' messages (unless admin).</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>STM_035</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Verify Thread in One-on-One Chat</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>User is logged in and one-on-one chat is open</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Verify thread works in one-on-one conversation</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Open a one-on-one chat.
 2. Reply in thread on a message.
 3. Send a reply.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>Thread should work correctly in one-on-one conversations.</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>STM_036</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Verify Thread in Group Chat</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>User is logged in and group chat is open</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Verify thread works in group conversation</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Open a group chat.
 2. Reply in thread on a message.
 3. Send a reply.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>Thread should work correctly in group conversations with multiple participants.</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>STM_037</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Verify multiple users can reply in same thread</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Have 3+ users reply in the same thread.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>All replies should display correctly with respective sender info.</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>STM_038</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n"/>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Verify thread scroll with many replies</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Open a thread with 50+ replies.
 2. Scroll through.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>All replies should load and scroll smoothly. Older replies should load on scroll up.</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
@@ -2364,7 +2424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2523,35 +2583,45 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>STM_051</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>STM_051</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify thread reply during network interruption</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>1. Start sending a thread reply.
 2. Disconnect network mid-send.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Message should show failed state with retry option. No partial/corrupted messages.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>

--- a/Send_Threaded_Message/Send_Threaded_Message_Test_Cases.xlsx
+++ b/Send_Threaded_Message/Send_Threaded_Message_Test_Cases.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -863,51 +863,73 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n"/>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>STM_014</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Verify Send Media in Thread</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and thread is open</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Verify attach button available in thread composer</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a thread.
+2. Observe thread composer.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Attach/attachment button should be available in the thread input area.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>STM_012</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Verify Send Text Message in Thread</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and thread is open</t>
-        </is>
-      </c>
+          <t>STM_015</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Verify empty message not sent in thread</t>
+          <t>Verify sending image in thread</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1. Open a thread.
-2. Leave input empty.
-3. Click send.</t>
+2. Click attach.
+3. Select an image.
+4. Send.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Empty message should not be sent. Send button should be disabled or no action.</t>
+          <t>Image should upload and display in the thread with thumbnail.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -919,30 +941,28 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>STM_013</t>
+          <t>STM_016</t>
         </is>
       </c>
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network disconnected</t>
-        </is>
-      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Verify text message fails in thread without network</t>
+          <t>Verify sending video in thread</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1. Disconnect network.
-2. Try to send text message in thread.</t>
+          <t>1. Open a thread.
+2. Click attach.
+3. Select a video.
+4. Send.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Error message should display or message should queue with retry option.</t>
+          <t>Video should upload and display in the thread with thumbnail and play icon.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -952,50 +972,63 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>STM_017</t>
+        </is>
+      </c>
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Verify sending audio in thread</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a thread.
+2. Click attach or record.
+3. Select/record audio.
+4. Send.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Audio message should display in thread with play button and duration.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>STM_014</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Verify Send Media in Thread</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and thread is open</t>
-        </is>
-      </c>
+          <t>STM_018</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Verify attach button available in thread composer</t>
+          <t>Verify sending document in thread</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
           <t>1. Open a thread.
-2. Observe thread composer.</t>
+2. Click attach.
+3. Select a document.
+4. Send.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Attach/attachment button should be available in the thread input area.</t>
+          <t>Document should upload and display with file icon, name, and size in thread.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1007,7 +1040,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>STM_015</t>
+          <t>STM_019</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
@@ -1015,32 +1048,30 @@
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Verify sending image in thread</t>
+          <t>Verify image preview in thread</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1. Open a thread.
-2. Click attach.
-3. Select an image.
-4. Send.</t>
+          <t>1. Send an image in thread.
+2. Tap on the image thumbnail.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Image should upload and display in the thread with thumbnail.</t>
+          <t>Full-size image preview should open.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>STM_016</t>
+          <t>STM_020</t>
         </is>
       </c>
       <c r="B19" s="2" t="n"/>
@@ -1048,65 +1079,74 @@
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Verify sending video in thread</t>
+          <t>Verify video playback in thread</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1. Open a thread.
-2. Click attach.
-3. Select a video.
-4. Send.</t>
+          <t>1. Send a video in thread.
+2. Tap play on the video.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Video should upload and display in the thread with thumbnail and play icon.</t>
+          <t>Video should play within the thread or in a media player.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>STM_017</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
+          <t>STM_024</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Verify Send Custom Message in Thread</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and thread is open</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Verify sending audio in thread</t>
+          <t>Verify sending sticker in thread</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1. Open a thread.
-2. Click attach or record.
-3. Select/record audio.
-4. Send.</t>
+2. Open sticker picker.
+3. Select a sticker.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Audio message should display in thread with play button and duration.</t>
+          <t>Sticker should be sent and display in the thread.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>STM_018</t>
+          <t>STM_025</t>
         </is>
       </c>
       <c r="B21" s="2" t="n"/>
@@ -1114,32 +1154,31 @@
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Verify sending document in thread</t>
+          <t>Verify sending GIF in thread</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Open a thread.
-2. Click attach.
-3. Select a document.
-4. Send.</t>
+2. Open GIF picker.
+3. Select a GIF.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Document should upload and display with file icon, name, and size in thread.</t>
+          <t>GIF should be sent and display/animate in the thread.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>STM_019</t>
+          <t>STM_026</t>
         </is>
       </c>
       <c r="B22" s="2" t="n"/>
@@ -1147,81 +1186,114 @@
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Verify image preview in thread</t>
+          <t>Verify sending location in thread (if supported)</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1. Send an image in thread.
-2. Tap on the image thumbnail.</t>
+          <t>1. Open a thread.
+2. Share location.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Full-size image preview should open.</t>
+          <t>Location message with map preview should display in the thread.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>STM_020</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
+          <t>STM_027</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Verify Thread Notifications</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and has participated in a thread</t>
+        </is>
+      </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Verify video playback in thread</t>
+          <t>Verify notification for new thread reply</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1. Send a video in thread.
-2. Tap play on the video.</t>
+          <t>1. Another user replies in a thread you participated in.
+2. Observe notifications.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Video should play within the thread or in a media player.</t>
+          <t>Notification should appear for the new thread reply.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>STM_028</t>
+        </is>
+      </c>
       <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread reply count updates in real-time</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1. Be on main chat.
+2. Another user replies in a thread.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Reply count on parent message should update in real-time.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>High / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>STM_021</t>
+          <t>STM_029</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Verify Send Media in Thread</t>
+          <t>Verify Thread Message Actions</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1231,53 +1303,50 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Verify file size limit in thread</t>
+          <t>Verify copy message in thread</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1. Open a thread.
-2. Try to attach a file exceeding size limit.</t>
+          <t>1. Long press on a text message in thread.
+2. Select 'Copy'.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Error message should display indicating file size limit exceeded.</t>
+          <t>Message text should be copied to clipboard.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>STM_022</t>
+          <t>STM_030</t>
         </is>
       </c>
       <c r="B26" s="2" t="n"/>
       <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network disconnected</t>
-        </is>
-      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Verify media upload fails in thread without network</t>
+          <t>Verify delete own message in thread</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1. Disconnect network.
-2. Try to send media in thread.</t>
+          <t>1. Long press on own message in thread.
+2. Select 'Delete'.
+3. Confirm.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Error message should display or upload should queue with retry option.</t>
+          <t>Message should be deleted from the thread. Reply count should update.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1289,51 +1358,70 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>STM_023</t>
+          <t>STM_031</t>
         </is>
       </c>
       <c r="B27" s="2" t="n"/>
       <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and thread is open</t>
-        </is>
-      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Verify unsupported file type in thread</t>
+          <t>Verify edit own message in thread</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1. Try to attach an unsupported file type in thread.</t>
+          <t>1. Long press on own text message in thread.
+2. Select 'Edit'.
+3. Modify and save.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Error message should display or file type should be rejected.</t>
+          <t>Message should update with new text and show 'edited' indicator.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n"/>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>STM_032</t>
+        </is>
+      </c>
       <c r="B28" s="2" t="n"/>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Verify react to message in thread</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1. Long press on a message in thread.
+2. Select a reaction.</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Reaction should appear below the message in the thread.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>STM_024</t>
+          <t>STM_035</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1343,73 +1431,81 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Verify Send Custom Message in Thread</t>
+          <t>Verify Thread in One-on-One Chat</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and thread is open</t>
+          <t>User is logged in and one-on-one chat is open</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Verify sending sticker in thread</t>
+          <t>Verify thread works in one-on-one conversation</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1. Open a thread.
-2. Open sticker picker.
-3. Select a sticker.</t>
+          <t>1. Open a one-on-one chat.
+2. Reply in thread on a message.
+3. Send a reply.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Sticker should be sent and display in the thread.</t>
+          <t>Thread should work correctly in one-on-one conversations.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>STM_025</t>
+          <t>STM_036</t>
         </is>
       </c>
       <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Verify Thread in Group Chat</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and group chat is open</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Verify sending GIF in thread</t>
+          <t>Verify thread works in group conversation</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1. Open a thread.
-2. Open GIF picker.
-3. Select a GIF.</t>
+          <t>1. Open a group chat.
+2. Reply in thread on a message.
+3. Send a reply.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>GIF should be sent and display/animate in the thread.</t>
+          <t>Thread should work correctly in group conversations with multiple participants.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>STM_026</t>
+          <t>STM_037</t>
         </is>
       </c>
       <c r="B31" s="2" t="n"/>
@@ -1417,114 +1513,80 @@
       <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Verify sending location in thread (if supported)</t>
+          <t>Verify multiple users can reply in same thread</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1. Open a thread.
-2. Share location.</t>
+          <t>1. Have 3+ users reply in the same thread.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Location message with map preview should display in the thread.</t>
+          <t>All replies should display correctly with respective sender info.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Low / Low</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>STM_027</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Verify Thread Notifications</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and has participated in a thread</t>
-        </is>
-      </c>
+          <t>STM_038</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Verify notification for new thread reply</t>
+          <t>Verify thread scroll with many replies</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1. Another user replies in a thread you participated in.
-2. Observe notifications.</t>
+          <t>1. Open a thread with 50+ replies.
+2. Scroll through.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Notification should appear for the new thread reply.</t>
+          <t>All replies should load and scroll smoothly. Older replies should load on scroll up.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>STM_028</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="n"/>
       <c r="B33" s="2" t="n"/>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Verify thread reply count updates in real-time</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>1. Be on main chat.
-2. Another user replies in a thread.</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Reply count on parent message should update in real-time.</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
-        </is>
-      </c>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>STM_029</t>
+          <t>STM_012</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Verify Thread Message Actions</t>
+          <t>Verify Send Text Message in Thread</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1534,50 +1596,54 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Verify copy message in thread</t>
+          <t>Verify empty message not sent in thread</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1. Long press on a text message in thread.
-2. Select 'Copy'.</t>
+          <t>1. Open a thread.
+2. Leave input empty.
+3. Click send.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Message text should be copied to clipboard.</t>
+          <t>Empty message should not be sent. Send button should be disabled or no action.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>STM_030</t>
+          <t>STM_013</t>
         </is>
       </c>
       <c r="B35" s="2" t="n"/>
       <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n"/>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, network disconnected</t>
+        </is>
+      </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Verify delete own message in thread</t>
+          <t>Verify text message fails in thread without network</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1. Long press on own message in thread.
-2. Select 'Delete'.
-3. Confirm.</t>
+          <t>1. Disconnect network.
+2. Try to send text message in thread.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Message should be deleted from the thread. Reply count should update.</t>
+          <t>Error message should display or message should queue with retry option.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1589,75 +1655,114 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>STM_031</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
+          <t>STM_021</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Verify Send Media in Thread</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and thread is open</t>
+        </is>
+      </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Verify edit own message in thread</t>
+          <t>Verify file size limit in thread</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1. Long press on own text message in thread.
-2. Select 'Edit'.
-3. Modify and save.</t>
+          <t>1. Open a thread.
+2. Try to attach a file exceeding size limit.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Message should update with new text and show 'edited' indicator.</t>
+          <t>Error message should display indicating file size limit exceeded.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>STM_032</t>
+          <t>STM_022</t>
         </is>
       </c>
       <c r="B37" s="2" t="n"/>
       <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, network disconnected</t>
+        </is>
+      </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Verify react to message in thread</t>
+          <t>Verify media upload fails in thread without network</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1. Long press on a message in thread.
-2. Select a reaction.</t>
+          <t>1. Disconnect network.
+2. Try to send media in thread.</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Reaction should appear below the message in the thread.</t>
+          <t>Error message should display or upload should queue with retry option.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n"/>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>STM_023</t>
+        </is>
+      </c>
       <c r="B38" s="2" t="n"/>
       <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="n"/>
-      <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2" t="n"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and thread is open</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Verify unsupported file type in thread</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>1. Try to attach an unsupported file type in thread.</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Error message should display or file type should be rejected.</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1730,161 +1835,6 @@
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
-      <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>STM_035</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Verify Thread in One-on-One Chat</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and one-on-one chat is open</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Verify thread works in one-on-one conversation</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a one-on-one chat.
-2. Reply in thread on a message.
-3. Send a reply.</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Thread should work correctly in one-on-one conversations.</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>STM_036</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n"/>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Verify Thread in Group Chat</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and group chat is open</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Verify thread works in group conversation</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a group chat.
-2. Reply in thread on a message.
-3. Send a reply.</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Thread should work correctly in group conversations with multiple participants.</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>STM_037</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Verify multiple users can reply in same thread</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>1. Have 3+ users reply in the same thread.</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>All replies should display correctly with respective sender info.</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>STM_038</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n"/>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Verify thread scroll with many replies</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a thread with 50+ replies.
-2. Scroll through.</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>All replies should load and scroll smoothly. Older replies should load on scroll up.</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
         </is>
       </c>
     </row>

--- a/Send_Threaded_Message/Send_Threaded_Message_Test_Cases.xlsx
+++ b/Send_Threaded_Message/Send_Threaded_Message_Test_Cases.xlsx
@@ -51,7 +51,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -65,11 +65,12 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -77,6 +78,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1564,277 +1569,701 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>STM_013</t>
+        </is>
+      </c>
       <c r="B33" s="2" t="n"/>
       <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="n"/>
-      <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2" t="n"/>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, network disconnected</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Verify text message fails in thread without network</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>1. Disconnect network.
+2. Try to send text message in thread.</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Error message should display or message should queue with retry option.</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>STM_022</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, network disconnected</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Verify media upload fails in thread without network</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>1. Disconnect network.
+2. Try to send media in thread.</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Error message should display or upload should queue with retry option.</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>STM_023</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and thread is open</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Verify unsupported file type in thread</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>1. Try to attach an unsupported file type in thread.</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Error message should display or file type should be rejected.</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>STM_034</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Verify cannot delete others' messages in thread</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>1. Long press on another user's message in thread.
+2. Observe menu.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>'Delete' option should NOT be available for other users' messages (unless admin).</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>THR_001</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Thread - Open Thread View</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Message with replies exists</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread view opens from message</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>1. Click 'View Replies' on a message
+2. Observe side panel</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Threaded messages side panel should open with thread header and message list</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>THR_002</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Thread - Thread Header Display</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Thread view open</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread header shows parent message</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a thread
+2. Observe header</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>CometChatThreadHeader should show parent message info with close button</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>THR_003</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Thread - Message List in Thread</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Thread view open</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread message list displays replies</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a thread
+2. Observe message list</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>CometChatMessageList should render with parentMessageId, showing thread replies</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>THR_004</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Thread - Compose Reply in Thread</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Thread view open, user not blocked</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Verify composing a reply in thread</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a thread
+2. Type message in thread composer
+3. Send</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>CometChatMessageComposer should be visible with parentMessageId, message sent as reply</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>THR_005</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Thread - Close Thread View</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Thread view open</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Verify closing thread view</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>1. Click close button on thread header
+2. Observe behavior</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Thread side panel should close, threadSearchMessage cleared</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>THR_006</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Thread - Subtitle Click Navigation</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Thread view open from search</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Verify clicking subtitle navigates to parent message</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>1. Open thread from search result
+2. Click subtitle in thread header</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Should navigate to parent message in main message list, thread closes on mobile</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>THR_007</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Thread - Search Keyword Highlighting</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Thread opened with search keyword</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Verify search keyword highlighting in thread</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>1. Search for a message
+2. Click result that's in a thread
+3. Observe thread</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Search keyword should be highlighted using CometChatTextHighlightFormatter</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>THR_008</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Thread - Go To Message ID</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Thread opened from search</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread scrolls to specific message</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>1. Search for a threaded message
+2. Click result
+3. Observe thread</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Thread should scroll to the specific message via goToMessageId</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
           <t>STM_012</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Verify Send Text Message in Thread</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>User is logged in and thread is open</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Verify empty message not sent in thread</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. Open a thread.
 2. Leave input empty.
 3. Click send.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Empty message should not be sent. Send button should be disabled or no action.</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>STM_013</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n"/>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network disconnected</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Verify text message fails in thread without network</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>1. Disconnect network.
-2. Try to send text message in thread.</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Error message should display or message should queue with retry option.</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>STM_021</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Verify Send Media in Thread</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>User is logged in and thread is open</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Verify file size limit in thread</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. Open a thread.
 2. Try to attach a file exceeding size limit.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>Error message should display indicating file size limit exceeded.</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>STM_022</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network disconnected</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Verify media upload fails in thread without network</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>1. Disconnect network.
-2. Try to send media in thread.</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Error message should display or upload should queue with retry option.</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>STM_023</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>STM_033</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Verify Thread Message Actions</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>User is logged in and thread is open</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Verify unsupported file type in thread</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>1. Try to attach an unsupported file type in thread.</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Error message should display or file type should be rejected.</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>STM_033</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Verify Thread Message Actions</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and thread is open</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Verify cannot edit others' messages in thread</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Long press on another user's message in thread.
 2. Observe menu.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>'Edit' option should NOT be available for other users' messages.</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>STM_034</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n"/>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Verify cannot delete others' messages in thread</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>1. Long press on another user's message in thread.
-2. Observe menu.</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>'Delete' option should NOT be available for other users' messages (unless admin).</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>THR_009</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Thread - Blocked User No Composer</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Thread open, user is blocked</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Verify composer hidden for blocked user in thread</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>1. Block a user
+2. Open thread in that conversation</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Composer should be hidden, 'Cannot send to blocked user' message shown with unblock link</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>THR_010</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Thread - Parent Message Deleted</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Thread open, parent message deleted</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread closes when parent deleted</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a thread
+2. Delete the parent message
+3. Observe</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Thread side panel should close automatically</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1847,530 +2276,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0070AD47"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>TestCase_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Sentiment</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Test Scenario</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Results</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>STM_039</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Integration: Thread with Message List</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Verify thread reply count updates in main message list</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>1. Reply in a thread.
-2. Close thread.
-3. Observe parent message in main chat.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Parent message should show updated reply count. Clicking count should reopen thread.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>STM_040</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Integration: Thread with Notifications</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Verify thread reply triggers notification for thread participants</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>1. User A replies in a thread.
-2. Check User B's notifications (who also replied in thread).</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>User B should receive notification for the new thread reply.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>STM_041</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Integration: Thread with Conversation List</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Verify thread reply updates conversation list preview</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1. Reply in a thread.
-2. Check conversation list.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Conversation preview should update to reflect the thread activity.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00FFC000"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>TestCase_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Sentiment</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Test Scenario</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Results</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>STM_042</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Regression: Threaded Message</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and thread is open</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Verify thread intact after editing parent message</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>1. Edit the parent message of a thread.
-2. Open thread.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Thread should remain intact. Parent message should show edited content. All replies preserved.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>STM_043</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Verify thread behavior after deleting parent message</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>1. Delete the parent message that has a thread.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Thread should be handled per policy — either deleted with parent or preserved with 'deleted message' parent.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>STM_044</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Verify thread after app restart</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a thread.
-2. Close and reopen app.
-3. Navigate back to thread.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Thread should load with all previous replies intact.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00FF0000"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>TestCase_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Sentiment</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Test Scenario</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Results</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>STM_045</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Security: Threaded Message</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Verify thread messages only visible to conversation participants</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>1. Login as a non-participant.
-2. Try to access thread messages.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Thread messages should not be accessible to non-participants of the conversation.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>STM_046</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Verify XSS prevention in thread messages</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>1. Send '&lt;img src=x onerror=alert(1)&gt;' in a thread reply.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>HTML should be escaped. No script execution.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>STM_047</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Verify thread message cannot be sent after being removed from group</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1. Get removed from a group.
-2. Try to send a thread reply in that group.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Message should fail with appropriate error.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2432,7 +2337,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>STM_048</t>
+          <t>STM_039</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -2442,138 +2347,190 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Edge Case: Threaded Message</t>
+          <t>Integration: Thread with Message List</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and thread is open</t>
+          <t>User is logged in and chat is open</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Verify thread with 500+ replies</t>
+          <t>Verify thread reply count updates in main message list</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>1. Open a thread with 500+ replies.
-2. Scroll through.</t>
+          <t>1. Reply in a thread.
+2. Close thread.
+3. Observe parent message in main chat.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>All replies should load via pagination. No performance issues.</t>
+          <t>Parent message should show updated reply count. Clicking count should reopen thread.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Medium / High</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>STM_049</t>
+          <t>STM_040</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Integration: Thread with Notifications</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Verify nested thread behavior (reply to a thread reply)</t>
+          <t>Verify thread reply triggers notification for thread participants</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>1. Try to reply to a specific message within a thread.</t>
+          <t>1. User A replies in a thread.
+2. Check User B's notifications (who also replied in thread).</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Should either allow nested reply or keep flat thread structure per design.</t>
+          <t>User B should receive notification for the new thread reply.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>STM_050</t>
+          <t>STM_041</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Integration: Thread with Conversation List</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Verify thread with mixed media types</t>
+          <t>Verify thread reply updates conversation list preview</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1. Send text, image, video, audio, and document in the same thread.</t>
+          <t>1. Reply in a thread.
+2. Check conversation list.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>All message types should display correctly within the thread.</t>
+          <t>Conversation preview should update to reflect the thread activity.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>THR_011</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Thread - Request Builder Config</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Thread view opening</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread messages request builder configuration</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a thread
+2. Monitor request builder</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>MessagesRequestBuilder should have parentMessageId set, limit 20, hideReplies true</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>STM_051</t>
+          <t>THR_012</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Thread - Unblock From Thread</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Blocked user, thread open</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Verify thread reply during network interruption</t>
+          <t>Verify unblock link works in thread</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1. Start sending a thread reply.
-2. Disconnect network mid-send.</t>
+          <t>1. Open thread with blocked user
+2. Click 'Click to unblock' link</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Message should show failed state with retry option. No partial/corrupted messages.</t>
+          <t>User should be unblocked, composer should reappear in thread</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2582,180 +2539,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="007030A0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>TestCase_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Sentiment</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Test Scenario</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Results</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>STM_052</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Boundary: Threaded Message</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and thread is open</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Verify thread with exactly 1 reply</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>1. Reply once in a thread.
-2. Observe thread and parent message.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Thread should show 1 reply. Parent message should show '1 Reply'.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>STM_053</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Verify thread reply with exactly 1 character</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>1. Send 'a' as a thread reply.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Single character reply should display correctly in thread.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>STM_054</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Verify thread reply at max character limit</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1. Send a thread reply at exactly the maximum character limit.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Reply should send successfully.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="0000B0F0"/>
+    <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2817,7 +2604,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>STM_055</t>
+          <t>STM_042</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -2827,28 +2614,28 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Equivalence Partitioning: Thread Contexts</t>
+          <t>Regression: Threaded Message</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in</t>
+          <t>User is logged in and thread is open</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Verify thread on a text message</t>
+          <t>Verify thread intact after editing parent message</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>1. Start a thread on a text message.
-2. Reply.</t>
+          <t>1. Edit the parent message of a thread.
+2. Open thread.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Thread should work correctly with text parent message.</t>
+          <t>Thread should remain intact. Parent message should show edited content. All replies preserved.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -2860,7 +2647,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>STM_056</t>
+          <t>STM_043</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -2868,18 +2655,17 @@
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Verify thread on an image message</t>
+          <t>Verify thread behavior after deleting parent message</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>1. Start a thread on an image message.
-2. Reply.</t>
+          <t>1. Delete the parent message that has a thread.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Thread should work correctly with image as parent. Image should display in thread header.</t>
+          <t>Thread should be handled per policy — either deleted with parent or preserved with 'deleted message' parent.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -2891,7 +2677,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>STM_057</t>
+          <t>STM_044</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -2899,6 +2685,845 @@
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>Verify thread after app restart</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a thread.
+2. Close and reopen app.
+3. Navigate back to thread.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Thread should load with all previous replies intact.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>THR_013</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Thread - Block/Unblock Updates Thread</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Thread open</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Verify block/unblock events update thread composer</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1. Open thread
+2. Block user from details
+3. Observe thread composer
+4. Unblock
+5. Observe</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Composer should hide on block and reappear on unblock</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FF0000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>STM_046</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Verify XSS prevention in thread messages</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1. Send '&lt;img src=x onerror=alert(1)&gt;' in a thread reply.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>HTML should be escaped. No script execution.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>STM_047</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread message cannot be sent after being removed from group</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>1. Get removed from a group.
+2. Try to send a thread reply in that group.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Message should fail with appropriate error.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>STM_045</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Security: Threaded Message</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread messages only visible to conversation participants</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as a non-participant.
+2. Try to access thread messages.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Thread messages should not be accessible to non-participants of the conversation.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>STM_048</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case: Threaded Message</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and thread is open</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread with 500+ replies</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a thread with 500+ replies.
+2. Scroll through.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>All replies should load via pagination. No performance issues.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>STM_049</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Verify nested thread behavior (reply to a thread reply)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>1. Try to reply to a specific message within a thread.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Should either allow nested reply or keep flat thread structure per design.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>STM_050</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread with mixed media types</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1. Send text, image, video, audio, and document in the same thread.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>All message types should display correctly within the thread.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>THR_014</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Thread - Switch Between Threads</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Multiple threads available</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Verify switching between different threads</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1. Open thread A
+2. Click View Replies on different message
+3. Observe</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Thread view should update to show new thread's messages</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n"/>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>STM_051</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread reply during network interruption</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1. Start sending a thread reply.
+2. Disconnect network mid-send.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Message should show failed state with retry option. No partial/corrupted messages.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>STM_052</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Boundary: Threaded Message</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and thread is open</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread with exactly 1 reply</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1. Reply once in a thread.
+2. Observe thread and parent message.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Thread should show 1 reply. Parent message should show '1 Reply'.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>STM_053</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread reply with exactly 1 character</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>1. Send 'a' as a thread reply.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Single character reply should display correctly in thread.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>STM_054</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread reply at max character limit</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1. Send a thread reply at exactly the maximum character limit.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Reply should send successfully.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0000B0F0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>STM_055</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning: Thread Contexts</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread on a text message</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1. Start a thread on a text message.
+2. Reply.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Thread should work correctly with text parent message.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>STM_056</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Verify thread on an image message</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>1. Start a thread on an image message.
+2. Reply.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Thread should work correctly with image as parent. Image should display in thread header.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>STM_057</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>Verify thread on a video message</t>
         </is>
       </c>
@@ -2950,6 +3575,16 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
